--- a/全聯貨號批次申請範本_UAT.xlsx
+++ b/全聯貨號批次申請範本_UAT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\全聯\Project\新預購\00企劃\批次提報\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\全聯工作PM\批次提報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCE785A-8A7A-4D2F-8DAB-00DA8DDBFFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C54DB8-2014-4E12-B73E-03E2BDE1C3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D7D6743F-4502-4948-8EC2-7833D446D963}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{D7D6743F-4502-4948-8EC2-7833D446D963}"/>
   </bookViews>
   <sheets>
     <sheet name="申請全聯貨號主表" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="113">
   <si>
     <t>自編流水號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,14 +416,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主圖7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主圖8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自編流水號
 (必須和主表一致)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -543,18 +535,6 @@
   </si>
   <si>
     <t>選填(指定廠商才可啓用)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>商品尺碼或規格圖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>試穿建議圖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=K1+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1194,27 +1174,27 @@
         <v>11</v>
       </c>
       <c r="L1" s="1">
-        <f>K1+1</f>
+        <f t="shared" ref="L1:Q1" si="1">K1+1</f>
         <v>12</v>
       </c>
       <c r="M1" s="1">
-        <f>L1+1</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="N1" s="1">
-        <f>M1+1</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="O1" s="1">
-        <f>N1+1</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="P1" s="25">
-        <f>O1+1</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="Q1" s="25">
-        <f>P1+1</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="R1" s="25">
@@ -1238,23 +1218,23 @@
         <v>22</v>
       </c>
       <c r="W1" s="9">
-        <f t="shared" ref="W1:AA1" si="1">V1+1</f>
+        <f t="shared" ref="W1:AA1" si="2">V1+1</f>
         <v>23</v>
       </c>
       <c r="X1" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="Y1" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="Z1" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="AA1" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="AB1" s="9">
@@ -1278,27 +1258,27 @@
         <v>32</v>
       </c>
       <c r="AG1" s="11">
-        <f t="shared" ref="AG1:AO1" si="2">AF1+1</f>
+        <f t="shared" ref="AG1:AO1" si="3">AF1+1</f>
         <v>33</v>
       </c>
       <c r="AH1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="AI1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="AJ1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="AK1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="AL1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="AM1" s="11">
@@ -1306,11 +1286,11 @@
         <v>39</v>
       </c>
       <c r="AN1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="AO1" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
       <c r="AP1" s="28">
@@ -1333,7 +1313,7 @@
         <v>42</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>69</v>
@@ -1345,7 +1325,7 @@
         <v>51</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>52</v>
@@ -1390,7 +1370,7 @@
         <v>77</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="X2" s="10" t="s">
         <v>11</v>
@@ -1423,7 +1403,7 @@
         <v>74</v>
       </c>
       <c r="AH2" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AI2" s="12" t="s">
         <v>70</v>
@@ -1432,10 +1412,10 @@
         <v>73</v>
       </c>
       <c r="AK2" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AL2" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AM2" s="12" t="s">
         <v>71</v>
@@ -1447,78 +1427,78 @@
         <v>67</v>
       </c>
       <c r="AP2" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AQ2" s="29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S3" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T3" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="U3" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="W3" s="10" t="s">
         <v>78</v>
@@ -1533,55 +1513,55 @@
         <v>78</v>
       </c>
       <c r="AA3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH3" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM3" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AB3" s="10" t="s">
+      <c r="AN3" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AC3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE3" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF3" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AG3" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH3" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AI3" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="AJ3" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK3" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL3" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM3" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN3" s="12" t="s">
-        <v>92</v>
-      </c>
       <c r="AO3" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AP3" s="30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AQ3" s="30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="46.8" x14ac:dyDescent="0.3">
@@ -1688,16 +1668,16 @@
         <v>49</v>
       </c>
       <c r="AI4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AJ4" s="13" t="s">
         <v>79</v>
       </c>
       <c r="AK4" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AL4" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AM4" s="6" t="s">
         <v>33</v>
@@ -1712,7 +1692,7 @@
         <v>26</v>
       </c>
       <c r="AQ4" s="31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1745,19 +1725,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31C746E-8A3A-4581-B6FD-DCA80DAD27F1}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="36.8984375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="20.69921875" style="14" customWidth="1"/>
-    <col min="12" max="12" width="27.59765625" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.59765625" style="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="36.8984375" style="14"/>
+    <col min="3" max="7" width="20.69921875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="27.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="36.8984375" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="22">
         <f>1</f>
         <v>1</v>
@@ -1767,7 +1747,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="20">
-        <f t="shared" ref="C1:N1" si="0">B1+1</f>
+        <f t="shared" ref="C1:J1" si="0">B1+1</f>
         <v>3</v>
       </c>
       <c r="D1" s="20">
@@ -1786,40 +1766,25 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H1" s="20">
-        <f t="shared" si="0"/>
+      <c r="H1" s="21">
+        <f>G1+1</f>
         <v>8</v>
       </c>
-      <c r="I1" s="20">
+      <c r="I1" s="21">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J1" s="20">
+      <c r="J1" s="21">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K1" s="20">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="M1" s="21" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N1" s="21" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>80</v>
@@ -1836,73 +1801,49 @@
       <c r="G2" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="L2" s="19" t="s">
+      <c r="H2" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="J2" s="19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>89</v>
       </c>
+      <c r="B3" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
@@ -1916,27 +1857,20 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="J4" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="7" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
